--- a/data/trans_orig/IP16A09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2452</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>2445</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38789</t>
+          <t>39860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4512</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72826</t>
+          <t>72635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79010</t>
+          <t>78923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83210</t>
+          <t>83157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158254</t>
+          <t>158769</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165746</t>
+          <t>165773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19867</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29770</t>
+          <t>30018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34622</t>
+          <t>34628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52337</t>
+          <t>51905</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57169</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4705</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14006</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116111</t>
+          <t>115866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123039</t>
+          <t>122929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>135919</t>
+          <t>135906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141900</t>
+          <t>141902</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254492</t>
+          <t>254460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>263793</t>
+          <t>264040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3175</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19677</t>
+          <t>19793</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45819</t>
+          <t>45273</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109557</t>
+          <t>109618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>114964</t>
+          <t>114981</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113462</t>
+          <t>113497</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>121304</t>
+          <t>121431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225640</t>
+          <t>226024</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>235093</t>
+          <t>235094</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40909</t>
+          <t>40643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>86271</t>
+          <t>85415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178321</t>
+          <t>179419</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185854</t>
+          <t>185759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180873</t>
+          <t>180978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>188838</t>
+          <t>188985</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>363259</t>
+          <t>363658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>373367</t>
+          <t>373604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1818</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>100232</t>
+          <t>100701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105345</t>
+          <t>105346</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91875</t>
+          <t>92196</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>97006</t>
+          <t>97008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>195093</t>
+          <t>194658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201783</t>
+          <t>201763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34736</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72336</t>
+          <t>71900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>567</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>707</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6388</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>157406</t>
+          <t>156684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161969</t>
+          <t>161966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141737</t>
+          <t>141108</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>147422</t>
+          <t>147418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>301701</t>
+          <t>300782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308416</t>
+          <t>308270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A09-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A09-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2949</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3045</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>13,81%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2431</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2445</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21450</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19099</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19003</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>86,19%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>62</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39860</t>
+          <t>39874</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4858</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4083</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1784</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8072</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7896</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,06%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,0%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4512</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>86380</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82811</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>76624</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72635</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>78923</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>72811</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>78856</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,94%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>90,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>86380</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83157</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158769</t>
+          <t>158483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165773</t>
+          <t>165662</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>517</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2943</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,05%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5248</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33283</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29939</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34627</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>22034</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19608</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20417</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,95%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>90,54%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33283</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30018</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>34628</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,38%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>85,12%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>83</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51905</t>
+          <t>51965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>57162</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7270</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9439</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2528</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9976</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,15%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1291</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7287</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>139921</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>135923</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>141905</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>120108</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>115866</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>122929</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>115329</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>122777</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,85%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,1%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>139921</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>135906</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>141902</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254460</t>
+          <t>255013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>264040</t>
+          <t>263984</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,107 +2325,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2792</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3059</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3163</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3102</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22245</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20060</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22245</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19793</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>86,61%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>68</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45273</t>
+          <t>45212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22852</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>25523</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>22852</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2668,72 +2668,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4975</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9925</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2558</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6112</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4975</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1963</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9897</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>12877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -2781,72 +2781,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>118419</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>113469</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>121420</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>113051</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>109618</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>114981</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>109497</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>114963</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,79%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>118419</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>113497</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>121431</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,97%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>226024</t>
+          <t>226126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>235094</t>
+          <t>235115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123394</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>167</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>115609</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>123394</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,107 +3011,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5216</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5114</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,06%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5676</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>44915</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40643</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>40745</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,94%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>88,85%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>126</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85415</t>
+          <t>86421</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>45232</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>45859</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>45232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3354,72 +3354,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10721</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7573</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1267</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2493</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10500</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -3467,72 +3467,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>185896</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>180757</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>188867</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>183491</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>179419</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>185759</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>179223</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>185725</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,13%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>185896</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>180978</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>188985</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>363658</t>
+          <t>363026</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>373604</t>
+          <t>373364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>191478</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>191478</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4041,47 +4041,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18856</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12775</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18856</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>12775</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,102 +4271,102 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5696</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2277</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>564</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5209</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5605</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5496</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>4376</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>8940</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>2,15%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>4376</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1838</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>8943</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4384,99 +4384,99 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>95593</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>91996</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>97000</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103633</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>100701</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>105346</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>100305</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>105340</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,85%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,47%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>95593</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>92196</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>97008</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>94,71%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>199225</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>194661</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>201611</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>97,85%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>199225</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>194658</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>201763</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
           <t>95,61%</t>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>97692</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105910</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>97692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4614,107 +4614,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3168</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3534</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3031</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -4727,74 +4727,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36959</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34491</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,59%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>36959</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>34125</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,14%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,62%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>109</t>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71900</t>
+          <t>72398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>37659</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>37770</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>37659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4962,67 +4962,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2277</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5852</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>9767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -5070,74 +5070,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>145326</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>141204</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>147420</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>160259</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>156684</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>161966</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>156588</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>161965</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,6%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,65%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>145326</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>141108</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>147418</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>452</t>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>300782</t>
+          <t>300894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308270</t>
+          <t>308356</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
